--- a/artfynd/A 55325-2025 artfynd.xlsx
+++ b/artfynd/A 55325-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
